--- a/public/downloads/RolingBimetallic2017.xlsx
+++ b/public/downloads/RolingBimetallic2017.xlsx
@@ -8,20 +8,22 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="MATLANTISv8" sheetId="8" r:id="rId8"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -53,10 +55,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -131,31 +133,52 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>Pt</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
+    <t>Ag</t>
+  </si>
+  <si>
+    <t>Au</t>
+  </si>
+  <si>
+    <t>Cu</t>
   </si>
   <si>
     <t>Ir</t>
   </si>
   <si>
-    <t>Cu</t>
+    <t>Pd</t>
+  </si>
+  <si>
+    <t>Pt</t>
   </si>
   <si>
     <t>Rh</t>
   </si>
   <si>
-    <t>Ag</t>
-  </si>
-  <si>
-    <t>Pd</t>
-  </si>
-  <si>
-    <t>Au</t>
+    <t>Os</t>
   </si>
   <si>
     <t>Re</t>
-  </si>
-  <si>
-    <t>Os</t>
   </si>
   <si>
     <t>Ru</t>
@@ -647,10 +670,10 @@
         <v>3850</v>
       </c>
       <c r="N3" s="5">
-        <v>9562.474247455597</v>
+        <v>9562474.247455597</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03189639106150007</v>
+        <v>31.89639106150006</v>
       </c>
       <c r="P3" s="5">
         <v>299798</v>
@@ -697,10 +720,10 @@
         <v>3850</v>
       </c>
       <c r="N4" s="5">
-        <v>20798.97544574738</v>
+        <v>20798975.44574738</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04640453235257441</v>
+        <v>46.40453235257441</v>
       </c>
       <c r="P4" s="5">
         <v>448210</v>
@@ -747,10 +770,10 @@
         <v>3850</v>
       </c>
       <c r="N5" s="5">
-        <v>38569.45289564133</v>
+        <v>38569452.89564133</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1320035350741528</v>
+        <v>132.0035350741528</v>
       </c>
       <c r="P5" s="5">
         <v>292185</v>
@@ -797,10 +820,10 @@
         <v>3850</v>
       </c>
       <c r="N6" s="5">
-        <v>29265.72682905197</v>
+        <v>29265726.82905197</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08459133796110592</v>
+        <v>84.59133796110592</v>
       </c>
       <c r="P6" s="5">
         <v>345966</v>
@@ -847,10 +870,10 @@
         <v>3000</v>
       </c>
       <c r="N7" s="5">
-        <v>27883.85217356682</v>
+        <v>27883852.17356682</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1527304864109834</v>
+        <v>152.7304864109834</v>
       </c>
       <c r="P7" s="5">
         <v>182569</v>
@@ -897,10 +920,10 @@
         <v>3850</v>
       </c>
       <c r="N8" s="5">
-        <v>25407.08738565445</v>
+        <v>25407087.38565445</v>
       </c>
       <c r="O8" s="4">
-        <v>0.08481440302861337</v>
+        <v>84.81440302861337</v>
       </c>
       <c r="P8" s="5">
         <v>299561</v>
@@ -926,7 +949,1186 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5188554135710317</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5184973090486337</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5146573629451394</v>
+      </c>
+      <c r="E3" s="4">
+        <v>75.82158467251635</v>
+      </c>
+      <c r="F3" s="4">
+        <v>84.75464448983631</v>
+      </c>
+      <c r="G3" s="5">
+        <v>414</v>
+      </c>
+      <c r="H3" s="5">
+        <v>411</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.5184973090486337</v>
+      </c>
+      <c r="O3" s="5">
+        <v>411</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0752053755855214</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07539360150883963</v>
+      </c>
+      <c r="R3" s="5">
+        <v>411</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5648652027308053</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5616925886059562</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5643310604606337</v>
+      </c>
+      <c r="E4" s="4">
+        <v>80.17976272634623</v>
+      </c>
+      <c r="F4" s="4">
+        <v>86.47656410422874</v>
+      </c>
+      <c r="G4" s="5">
+        <v>414</v>
+      </c>
+      <c r="H4" s="5">
+        <v>400</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>14</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>14</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.5616925886059562</v>
+      </c>
+      <c r="O4" s="5">
+        <v>400</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08731094997863934</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07688477173461215</v>
+      </c>
+      <c r="R4" s="5">
+        <v>400</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1378598067940482</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1308865974339846</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1289138802666049</v>
+      </c>
+      <c r="E5" s="4">
+        <v>82.37889841927164</v>
+      </c>
+      <c r="F5" s="4">
+        <v>88.70308227690884</v>
+      </c>
+      <c r="G5" s="5">
+        <v>414</v>
+      </c>
+      <c r="H5" s="5">
+        <v>408</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>5</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1242944072788553</v>
+      </c>
+      <c r="O5" s="5">
+        <v>408</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07816075752596079</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0693761352816516</v>
+      </c>
+      <c r="R5" s="5">
+        <v>408</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.455827709023149</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.4555737818845641</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.4536994611019958</v>
+      </c>
+      <c r="E6" s="4">
+        <v>88.2406585822735</v>
+      </c>
+      <c r="F6" s="4">
+        <v>91.90107966151191</v>
+      </c>
+      <c r="G6" s="5">
+        <v>414</v>
+      </c>
+      <c r="H6" s="5">
+        <v>410</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.4555737818845641</v>
+      </c>
+      <c r="O6" s="5">
+        <v>410</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1053761396906299</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1038553732898776</v>
+      </c>
+      <c r="R6" s="5">
+        <v>410</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.6169236078604531</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.6169236078604531</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.6111909271538402</v>
+      </c>
+      <c r="E7" s="4">
+        <v>79.79008511617208</v>
+      </c>
+      <c r="F7" s="4">
+        <v>87.30252137167805</v>
+      </c>
+      <c r="G7" s="5">
+        <v>414</v>
+      </c>
+      <c r="H7" s="5">
+        <v>414</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>-0.6169236078604531</v>
+      </c>
+      <c r="O7" s="5">
+        <v>414</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.07399027816554271</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.07399027816554271</v>
+      </c>
+      <c r="R7" s="5">
+        <v>414</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.6091795622448668</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.6088679874994194</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.6075577839213799</v>
+      </c>
+      <c r="E8" s="4">
+        <v>84.68582602122974</v>
+      </c>
+      <c r="F8" s="4">
+        <v>90.16346226588432</v>
+      </c>
+      <c r="G8" s="5">
+        <v>414</v>
+      </c>
+      <c r="H8" s="5">
+        <v>412</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>-0.6088679874994194</v>
+      </c>
+      <c r="O8" s="5">
+        <v>412</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.0769864178802785</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.07704705111121377</v>
+      </c>
+      <c r="R8" s="5">
+        <v>412</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.4475448117795867</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.4478868299638068</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.4462560962221884</v>
+      </c>
+      <c r="E9" s="4">
+        <v>86.16130993460187</v>
+      </c>
+      <c r="F9" s="4">
+        <v>90.7109392730934</v>
+      </c>
+      <c r="G9" s="5">
+        <v>414</v>
+      </c>
+      <c r="H9" s="5">
+        <v>412</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <v>-0.4478868299638068</v>
+      </c>
+      <c r="O9" s="5">
+        <v>412</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.08733630893597169</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.08741659313404158</v>
+      </c>
+      <c r="R9" s="5">
+        <v>412</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0.606762317594003</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.5883905509432389</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.5771975737944819</v>
+      </c>
+      <c r="E10" s="4">
+        <v>80.92837134853963</v>
+      </c>
+      <c r="F10" s="4">
+        <v>86.583667023855</v>
+      </c>
+      <c r="G10" s="5">
+        <v>238</v>
+      </c>
+      <c r="H10" s="5">
+        <v>221</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>17</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>16</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-0.5840924264301415</v>
+      </c>
+      <c r="O10" s="5">
+        <v>221</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.2298057931934378</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1954150931274415</v>
+      </c>
+      <c r="R10" s="5">
+        <v>221</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.7254275845013083</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.7316886342649053</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.7132414449795202</v>
+      </c>
+      <c r="E11" s="4">
+        <v>81.74555536500328</v>
+      </c>
+      <c r="F11" s="4">
+        <v>87.16569849415995</v>
+      </c>
+      <c r="G11" s="5">
+        <v>238</v>
+      </c>
+      <c r="H11" s="5">
+        <v>221</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>17</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>17</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>-0.724336472735716</v>
+      </c>
+      <c r="O11" s="5">
+        <v>221</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.261484485882171</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.2543809865294819</v>
+      </c>
+      <c r="R11" s="5">
+        <v>221</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0.3632485900840341</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.3669408583029517</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.3656999707447172</v>
+      </c>
+      <c r="E12" s="4">
+        <v>82.61618933287602</v>
+      </c>
+      <c r="F12" s="4">
+        <v>88.98905871073214</v>
+      </c>
+      <c r="G12" s="5">
+        <v>238</v>
+      </c>
+      <c r="H12" s="5">
+        <v>235</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>3</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>3</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4">
+        <v>-0.3451128632803082</v>
+      </c>
+      <c r="O12" s="5">
+        <v>235</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.1979437829773134</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.1964072869690227</v>
+      </c>
+      <c r="R12" s="5">
+        <v>235</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.3985710691711827</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.3990836960834979</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.393713282330131</v>
+      </c>
+      <c r="E13" s="4">
+        <v>82.35608529125938</v>
+      </c>
+      <c r="F13" s="4">
+        <v>88.50328050683365</v>
+      </c>
+      <c r="G13" s="5">
+        <v>238</v>
+      </c>
+      <c r="H13" s="5">
+        <v>237</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4">
+        <v>-0.3990836960834979</v>
+      </c>
+      <c r="O13" s="5">
+        <v>237</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.0602776503404534</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.06001719652277169</v>
+      </c>
+      <c r="R13" s="5">
+        <v>237</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>97.37662337662337</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.02597402597402598</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.597402597402597</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.597402597402597</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1388211128205677</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1323196785967917</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1403911900510892</v>
+      </c>
+      <c r="K3" s="4">
+        <v>84.33587772771443</v>
+      </c>
+      <c r="L3" s="4">
+        <v>89.43418170196756</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3850</v>
+      </c>
+      <c r="N3" s="5">
+        <v>9562474.247455597</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.89639106150006</v>
+      </c>
+      <c r="P3" s="5">
+        <v>299798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>92.44155844155844</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="D4" s="3">
+        <v>7.038961038961039</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.6233766233766234</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6.415584415584416</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.185452740684963</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1639882052150507</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.1773068190772146</v>
+      </c>
+      <c r="K4" s="4">
+        <v>80.13933209647477</v>
+      </c>
+      <c r="L4" s="4">
+        <v>84.39042679915154</v>
+      </c>
+      <c r="M4" s="5">
+        <v>3850</v>
+      </c>
+      <c r="N4" s="5">
+        <v>20798975.44574738</v>
+      </c>
+      <c r="O4" s="4">
+        <v>46.40453235257441</v>
+      </c>
+      <c r="P4" s="5">
+        <v>448210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>97.94805194805195</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.1558441558441558</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.896103896103896</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.05194805194805195</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.844155844155844</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1114985961291513</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1066641031507543</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1112005943562614</v>
+      </c>
+      <c r="K5" s="4">
+        <v>84.35158582913679</v>
+      </c>
+      <c r="L5" s="4">
+        <v>89.45670705133651</v>
+      </c>
+      <c r="M5" s="5">
+        <v>3850</v>
+      </c>
+      <c r="N5" s="5">
+        <v>38569452.89564133</v>
+      </c>
+      <c r="O5" s="4">
+        <v>132.0035350741528</v>
+      </c>
+      <c r="P5" s="5">
+        <v>292185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>97.45454545454545</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.545454545454545</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.467532467532468</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2015023606554979</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1955513020040301</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1886268643923585</v>
+      </c>
+      <c r="K6" s="4">
+        <v>83.78498984009188</v>
+      </c>
+      <c r="L6" s="4">
+        <v>87.86982480606683</v>
+      </c>
+      <c r="M6" s="5">
+        <v>3850</v>
+      </c>
+      <c r="N6" s="5">
+        <v>29265726.82905197</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.59133796110592</v>
+      </c>
+      <c r="P6" s="5">
+        <v>345966</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>99.06666666666666</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.08282890307499147</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.08147162735895155</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.08269626877643337</v>
+      </c>
+      <c r="K7" s="4">
+        <v>88.79582766439866</v>
+      </c>
+      <c r="L7" s="4">
+        <v>92.16344146159609</v>
+      </c>
+      <c r="M7" s="5">
+        <v>3000</v>
+      </c>
+      <c r="N7" s="5">
+        <v>27883852.17356682</v>
+      </c>
+      <c r="O7" s="4">
+        <v>152.7304864109834</v>
+      </c>
+      <c r="P7" s="5">
+        <v>182569</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>98.20779220779221</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.07792207792207792</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.02597402597402598</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.688311688311688</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1091717937255368</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1033595777215337</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.107101278043049</v>
+      </c>
+      <c r="K8" s="4">
+        <v>82.32848308154443</v>
+      </c>
+      <c r="L8" s="4">
+        <v>88.38457537987748</v>
+      </c>
+      <c r="M8" s="5">
+        <v>3850</v>
+      </c>
+      <c r="N8" s="5">
+        <v>25407087.38565445</v>
+      </c>
+      <c r="O8" s="4">
+        <v>84.81440302861337</v>
+      </c>
+      <c r="P8" s="5">
+        <v>299561</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1084,16 +2286,16 @@
         <v>13</v>
       </c>
       <c r="K4" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="M4" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N4" s="5">
-        <v>169</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -1128,16 +2330,16 @@
         <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -1263,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
@@ -1285,9 +2487,368 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>3749</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>100</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>100</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>64</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>3559</v>
+      </c>
+      <c r="C4" s="5">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5">
+        <v>271</v>
+      </c>
+      <c r="E4" s="5">
+        <v>24</v>
+      </c>
+      <c r="F4" s="5">
+        <v>247</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>24</v>
+      </c>
+      <c r="I4" s="5">
+        <v>11</v>
+      </c>
+      <c r="J4" s="5">
+        <v>13</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>129</v>
+      </c>
+      <c r="M4" s="5">
+        <v>2</v>
+      </c>
+      <c r="N4" s="5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3771</v>
+      </c>
+      <c r="C5" s="5">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5">
+        <v>73</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>71</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>37</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>3752</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>98</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>95</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
+        <v>57</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2972</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>27</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>27</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>12</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3781</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>66</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>65</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>40</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1298,9 +2859,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1334,8 +2901,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1357,92 +2932,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3101505735049176</v>
+        <v>0.619217522100952</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3101505735049176</v>
+        <v>0.6171568810984206</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3150045462584247</v>
+        <v>0.6168123278322417</v>
       </c>
       <c r="E3" s="4">
-        <v>87.65996253573893</v>
+        <v>78.43849617141544</v>
       </c>
       <c r="F3" s="4">
-        <v>91.67585297582379</v>
+        <v>86.6291919290171</v>
       </c>
       <c r="G3" s="5">
         <v>414</v>
       </c>
       <c r="H3" s="5">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6171568810984206</v>
+      </c>
+      <c r="O3" s="5">
+        <v>410</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1048481294829384</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1031549369442885</v>
+      </c>
+      <c r="R3" s="5">
+        <v>410</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
-        <v>0.628132138001081</v>
+        <v>0.3441668792000676</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6278157783103026</v>
+        <v>0.3408513401571432</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6300251471790899</v>
+        <v>0.3454353403116794</v>
       </c>
       <c r="E4" s="4">
-        <v>87.67581911991853</v>
+        <v>81.89260245160801</v>
       </c>
       <c r="F4" s="4">
-        <v>91.37348831177395</v>
+        <v>87.94688692193822</v>
       </c>
       <c r="G4" s="5">
         <v>414</v>
       </c>
       <c r="H4" s="5">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3386690345142478</v>
+      </c>
+      <c r="O4" s="5">
+        <v>398</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09849228451952907</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0876522346411326</v>
+      </c>
+      <c r="R4" s="5">
+        <v>398</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.7549490729643847</v>
@@ -1480,107 +3109,161 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.7565910875890168</v>
+      </c>
+      <c r="O5" s="5">
+        <v>400</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09175547078466448</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0876090614348233</v>
+      </c>
+      <c r="R5" s="5">
+        <v>400</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4604019160847448</v>
+        <v>0.628132138001081</v>
       </c>
       <c r="C6" s="4">
-        <v>0.460102097674708</v>
+        <v>0.6278157783103026</v>
       </c>
       <c r="D6" s="4">
-        <v>0.4678539364073879</v>
+        <v>0.6300251471790899</v>
       </c>
       <c r="E6" s="4">
-        <v>90.36889151795985</v>
+        <v>87.67581911991853</v>
       </c>
       <c r="F6" s="4">
-        <v>93.13580066789869</v>
+        <v>91.37348831177395</v>
       </c>
       <c r="G6" s="5">
         <v>414</v>
       </c>
       <c r="H6" s="5">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.6277738551492573</v>
+      </c>
+      <c r="O6" s="5">
+        <v>405</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.150043543400691</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1444384593738349</v>
+      </c>
+      <c r="R6" s="5">
+        <v>405</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
-        <v>0.619217522100952</v>
+        <v>0.8950465178089574</v>
       </c>
       <c r="C7" s="4">
-        <v>0.6171568810984206</v>
+        <v>0.8950465178089574</v>
       </c>
       <c r="D7" s="4">
-        <v>0.6168123278322417</v>
+        <v>0.9001368719543944</v>
       </c>
       <c r="E7" s="4">
-        <v>78.43849617141544</v>
+        <v>84.88768937526702</v>
       </c>
       <c r="F7" s="4">
-        <v>86.6291919290171</v>
+        <v>90.33227420592463</v>
       </c>
       <c r="G7" s="5">
         <v>414</v>
       </c>
       <c r="H7" s="5">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.8950465178089574</v>
+      </c>
+      <c r="O7" s="5">
+        <v>414</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.09880561607651323</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.09880561607651323</v>
+      </c>
+      <c r="R7" s="5">
+        <v>414</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
-        <v>0.8950465178089574</v>
+        <v>0.3101505735049176</v>
       </c>
       <c r="C8" s="4">
-        <v>0.8950465178089574</v>
+        <v>0.3101505735049176</v>
       </c>
       <c r="D8" s="4">
-        <v>0.9001368719543944</v>
+        <v>0.3150045462584247</v>
       </c>
       <c r="E8" s="4">
-        <v>84.88768937526702</v>
+        <v>87.65996253573893</v>
       </c>
       <c r="F8" s="4">
-        <v>90.33227420592463</v>
+        <v>91.67585297582379</v>
       </c>
       <c r="G8" s="5">
         <v>414</v>
@@ -1603,133 +3286,205 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.3066929368724008</v>
+      </c>
+      <c r="O8" s="5">
+        <v>414</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1141373922749373</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1141373922749373</v>
+      </c>
+      <c r="R8" s="5">
+        <v>414</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
-        <v>0.3441668792000676</v>
+        <v>0.4604019160847448</v>
       </c>
       <c r="C9" s="4">
-        <v>0.3408513401571432</v>
+        <v>0.460102097674708</v>
       </c>
       <c r="D9" s="4">
-        <v>0.3454353403116794</v>
+        <v>0.4678539364073879</v>
       </c>
       <c r="E9" s="4">
-        <v>81.89260245160801</v>
+        <v>90.36889151795985</v>
       </c>
       <c r="F9" s="4">
-        <v>87.94688692193822</v>
+        <v>93.13580066789869</v>
       </c>
       <c r="G9" s="5">
         <v>414</v>
       </c>
       <c r="H9" s="5">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="I9" s="5">
         <v>0</v>
       </c>
       <c r="J9" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.4598708518236438</v>
+      </c>
+      <c r="O9" s="5">
+        <v>410</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1090021912147836</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.108914594878793</v>
+      </c>
+      <c r="R9" s="5">
+        <v>410</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>1.883457694156798</v>
+        <v>1.206442810785868</v>
       </c>
       <c r="C10" s="4">
-        <v>1.641689555212195</v>
+        <v>1.223503400698428</v>
       </c>
       <c r="D10" s="4">
-        <v>1.85887649021526</v>
+        <v>1.180022493928866</v>
       </c>
       <c r="E10" s="4">
-        <v>82.92531298233591</v>
+        <v>82.28877265191817</v>
       </c>
       <c r="F10" s="4">
-        <v>86.96304024965437</v>
+        <v>86.62018498674388</v>
       </c>
       <c r="G10" s="5">
         <v>238</v>
       </c>
       <c r="H10" s="5">
-        <v>119</v>
+        <v>218</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M10" s="5">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-1.223503400698428</v>
+      </c>
+      <c r="O10" s="5">
+        <v>218</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.2489867211580931</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.2298870836623952</v>
+      </c>
+      <c r="R10" s="5">
+        <v>218</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>1.206442810785868</v>
+        <v>1.883457694156798</v>
       </c>
       <c r="C11" s="4">
-        <v>1.223503400698428</v>
+        <v>1.641689555212195</v>
       </c>
       <c r="D11" s="4">
-        <v>1.180022493928866</v>
+        <v>1.85887649021526</v>
       </c>
       <c r="E11" s="4">
-        <v>82.28877265191817</v>
+        <v>82.92531298233591</v>
       </c>
       <c r="F11" s="4">
-        <v>86.62018498674388</v>
+        <v>86.96304024965437</v>
       </c>
       <c r="G11" s="5">
         <v>238</v>
       </c>
       <c r="H11" s="5">
-        <v>218</v>
+        <v>119</v>
       </c>
       <c r="I11" s="5">
         <v>0</v>
       </c>
       <c r="J11" s="5">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+        <v>95</v>
+      </c>
+      <c r="N11" s="4">
+        <v>-1.911452387340421</v>
+      </c>
+      <c r="O11" s="5">
+        <v>214</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.3339042878513063</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.3139127126206388</v>
+      </c>
+      <c r="R11" s="5">
+        <v>214</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4">
         <v>0.6315519406261141</v>
@@ -1767,10 +3522,28 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-0.6275264175708274</v>
+      </c>
+      <c r="O12" s="5">
+        <v>229</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.2300108544581959</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.2271776876370573</v>
+      </c>
+      <c r="R12" s="5">
+        <v>229</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4">
         <v>0.9836849165507385</v>
@@ -1808,9 +3581,27 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
+      <c r="N13" s="4">
+        <v>-0.9845304149747647</v>
+      </c>
+      <c r="O13" s="5">
+        <v>237</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.09839329816688312</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.09795939383459899</v>
+      </c>
+      <c r="R13" s="5">
+        <v>237</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1821,14 +3612,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1839,9 +3631,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1875,8 +3673,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1898,92 +3704,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3584883824344575</v>
+        <v>0.3555073241472808</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3591340947864738</v>
+        <v>0.3460120203509739</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3762127413711682</v>
+        <v>0.3516797038425812</v>
       </c>
       <c r="E3" s="4">
-        <v>84.21645469782116</v>
+        <v>75.56262118373913</v>
       </c>
       <c r="F3" s="4">
-        <v>87.9312972149274</v>
+        <v>82.29195711614624</v>
       </c>
       <c r="G3" s="5">
         <v>414</v>
       </c>
       <c r="H3" s="5">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3430541603041283</v>
+      </c>
+      <c r="O3" s="5">
+        <v>382</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1286152485115248</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1071317388045918</v>
+      </c>
+      <c r="R3" s="5">
+        <v>382</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4834941205746811</v>
+        <v>0.1273910283495094</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4816262651527224</v>
+        <v>0.109717570270417</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4901965210445497</v>
+        <v>0.1268845121728181</v>
       </c>
       <c r="E4" s="4">
-        <v>84.18063360610003</v>
+        <v>79.94692563015579</v>
       </c>
       <c r="F4" s="4">
-        <v>86.84045002107607</v>
+        <v>83.138745690541</v>
       </c>
       <c r="G4" s="5">
         <v>414</v>
       </c>
       <c r="H4" s="5">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.01913949341708959</v>
+      </c>
+      <c r="O4" s="5">
+        <v>379</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.125340800970456</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.107831507787545</v>
+      </c>
+      <c r="R4" s="5">
+        <v>379</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.4811540868544579</v>
@@ -2021,256 +3881,382 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.4672604550334108</v>
+      </c>
+      <c r="O5" s="5">
+        <v>367</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1415639921195436</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1109497593934344</v>
+      </c>
+      <c r="R5" s="5">
+        <v>367</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2284870856344807</v>
+        <v>0.4834941205746811</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2258673089733452</v>
+        <v>0.4816262651527224</v>
       </c>
       <c r="D6" s="4">
-        <v>0.2116917683147958</v>
+        <v>0.4901965210445497</v>
       </c>
       <c r="E6" s="4">
-        <v>86.20625061618885</v>
+        <v>84.18063360610003</v>
       </c>
       <c r="F6" s="4">
-        <v>88.70573009543023</v>
+        <v>86.84045002107607</v>
       </c>
       <c r="G6" s="5">
         <v>414</v>
       </c>
       <c r="H6" s="5">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="5">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.4754017430141103</v>
+      </c>
+      <c r="O6" s="5">
+        <v>386</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2058103639317244</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1951320153239044</v>
+      </c>
+      <c r="R6" s="5">
+        <v>386</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
-        <v>0.3555073241472808</v>
+        <v>0.4427801415277807</v>
       </c>
       <c r="C7" s="4">
-        <v>0.3460120203509739</v>
+        <v>0.4424592267163273</v>
       </c>
       <c r="D7" s="4">
-        <v>0.3516797038425812</v>
+        <v>0.4542367638350552</v>
       </c>
       <c r="E7" s="4">
-        <v>75.56262118373913</v>
+        <v>80.5304972230437</v>
       </c>
       <c r="F7" s="4">
-        <v>82.29195711614624</v>
+        <v>85.67270801586561</v>
       </c>
       <c r="G7" s="5">
         <v>414</v>
       </c>
       <c r="H7" s="5">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.4387133721418743</v>
+      </c>
+      <c r="O7" s="5">
+        <v>412</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.134259083079741</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1345701697910732</v>
+      </c>
+      <c r="R7" s="5">
+        <v>412</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
-        <v>0.4427801415277807</v>
+        <v>0.3584883824344575</v>
       </c>
       <c r="C8" s="4">
-        <v>0.4424592267163273</v>
+        <v>0.3591340947864738</v>
       </c>
       <c r="D8" s="4">
-        <v>0.4542367638350552</v>
+        <v>0.3762127413711682</v>
       </c>
       <c r="E8" s="4">
-        <v>80.5304972230437</v>
+        <v>84.21645469782116</v>
       </c>
       <c r="F8" s="4">
-        <v>85.67270801586561</v>
+        <v>87.9312972149274</v>
       </c>
       <c r="G8" s="5">
         <v>414</v>
       </c>
       <c r="H8" s="5">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.3436394967250757</v>
+      </c>
+      <c r="O8" s="5">
+        <v>406</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.1715901720914971</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.1708752698193488</v>
+      </c>
+      <c r="R8" s="5">
+        <v>406</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
-        <v>0.1273910283495094</v>
+        <v>0.2284870856344807</v>
       </c>
       <c r="C9" s="4">
-        <v>0.109717570270417</v>
+        <v>0.2258673089733452</v>
       </c>
       <c r="D9" s="4">
-        <v>0.1268845121728181</v>
+        <v>0.2116917683147958</v>
       </c>
       <c r="E9" s="4">
-        <v>79.94692563015579</v>
+        <v>86.20625061618885</v>
       </c>
       <c r="F9" s="4">
-        <v>83.138745690541</v>
+        <v>88.70573009543023</v>
       </c>
       <c r="G9" s="5">
         <v>414</v>
       </c>
       <c r="H9" s="5">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="I9" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K9" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L9" s="5">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>0.1861534327419868</v>
+      </c>
+      <c r="O9" s="5">
+        <v>401</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.1661804797535738</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.1627924239848572</v>
+      </c>
+      <c r="R9" s="5">
+        <v>401</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>1.465272126938031</v>
+        <v>1.251666751764639</v>
       </c>
       <c r="C10" s="4">
-        <v>1.423560887236261</v>
+        <v>1.273722529039068</v>
       </c>
       <c r="D10" s="4">
-        <v>1.423082657909073</v>
+        <v>1.213494010336174</v>
       </c>
       <c r="E10" s="4">
-        <v>75.98053507117109</v>
+        <v>77.27262333504828</v>
       </c>
       <c r="F10" s="4">
-        <v>79.73779444663745</v>
+        <v>80.45443009418391</v>
       </c>
       <c r="G10" s="5">
         <v>238</v>
       </c>
       <c r="H10" s="5">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="I10" s="5">
+        <v>2</v>
+      </c>
+      <c r="J10" s="5">
+        <v>42</v>
+      </c>
+      <c r="K10" s="5">
         <v>3</v>
       </c>
-      <c r="J10" s="5">
-        <v>77</v>
-      </c>
-      <c r="K10" s="5">
-        <v>5</v>
-      </c>
       <c r="L10" s="5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M10" s="5">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+        <v>2</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-1.28007817091255</v>
+      </c>
+      <c r="O10" s="5">
+        <v>196</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.325482934968839</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.2757062423613096</v>
+      </c>
+      <c r="R10" s="5">
+        <v>196</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>1.251666751764639</v>
+        <v>1.465272126938031</v>
       </c>
       <c r="C11" s="4">
-        <v>1.273722529039068</v>
+        <v>1.423560887236261</v>
       </c>
       <c r="D11" s="4">
-        <v>1.213494010336174</v>
+        <v>1.423082657909073</v>
       </c>
       <c r="E11" s="4">
-        <v>77.27262333504828</v>
+        <v>75.98053507117109</v>
       </c>
       <c r="F11" s="4">
-        <v>80.45443009418391</v>
+        <v>79.73779444663745</v>
       </c>
       <c r="G11" s="5">
         <v>238</v>
       </c>
       <c r="H11" s="5">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="I11" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="5">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="K11" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L11" s="5">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="M11" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+        <v>27</v>
+      </c>
+      <c r="N11" s="4">
+        <v>-1.535500097217541</v>
+      </c>
+      <c r="O11" s="5">
+        <v>185</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.4268946702771889</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.3428111570419144</v>
+      </c>
+      <c r="R11" s="5">
+        <v>185</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4">
         <v>0.5735793536922407</v>
@@ -2308,10 +4294,28 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-0.5289446822505075</v>
+      </c>
+      <c r="O12" s="5">
+        <v>210</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.2582030110837319</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.2371740685569465</v>
+      </c>
+      <c r="R12" s="5">
+        <v>210</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4">
         <v>0.7922578910763182</v>
@@ -2349,9 +4353,27 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
+      <c r="N13" s="4">
+        <v>-0.7927533314546191</v>
+      </c>
+      <c r="O13" s="5">
+        <v>235</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.1222847344579301</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1210168663918271</v>
+      </c>
+      <c r="R13" s="5">
+        <v>235</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2362,14 +4384,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2380,9 +4403,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -2416,8 +4445,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2439,92 +4476,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6020871478541189</v>
+        <v>0.5869560280937205</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5999431218739132</v>
+        <v>0.5859619123285809</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6009939719080365</v>
+        <v>0.5860116337094031</v>
       </c>
       <c r="E3" s="4">
-        <v>86.06181603076007</v>
+        <v>78.96808965131946</v>
       </c>
       <c r="F3" s="4">
-        <v>90.96537301818893</v>
+        <v>86.70489792389455</v>
       </c>
       <c r="G3" s="5">
         <v>414</v>
       </c>
       <c r="H3" s="5">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5859619123285809</v>
+      </c>
+      <c r="O3" s="5">
+        <v>411</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06768773366105831</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06718043262508594</v>
+      </c>
+      <c r="R3" s="5">
+        <v>411</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
-        <v>0.507544732360799</v>
+        <v>0.5002520384031504</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5025788962191692</v>
+        <v>0.5020186524035499</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5043109121068429</v>
+        <v>0.5038475682994127</v>
       </c>
       <c r="E4" s="4">
-        <v>88.91887672943578</v>
+        <v>84.31175851983306</v>
       </c>
       <c r="F4" s="4">
-        <v>92.19012417728665</v>
+        <v>89.15215770190966</v>
       </c>
       <c r="G4" s="5">
         <v>414</v>
       </c>
       <c r="H4" s="5">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.5020186524035499</v>
+      </c>
+      <c r="O4" s="5">
+        <v>404</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07932949976023061</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07309789000375318</v>
+      </c>
+      <c r="R4" s="5">
+        <v>404</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.5780532802110152</v>
@@ -2562,116 +4653,170 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.5817540741696292</v>
+      </c>
+      <c r="O5" s="5">
+        <v>401</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06888047332264895</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06361059985909026</v>
+      </c>
+      <c r="R5" s="5">
+        <v>401</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4147537809294656</v>
+        <v>0.507544732360799</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4143966357689273</v>
+        <v>0.5025788962191692</v>
       </c>
       <c r="D6" s="4">
-        <v>0.4176679751630732</v>
+        <v>0.5043109121068429</v>
       </c>
       <c r="E6" s="4">
-        <v>89.94166748825137</v>
+        <v>88.91887672943578</v>
       </c>
       <c r="F6" s="4">
-        <v>92.91640999038148</v>
+        <v>92.19012417728665</v>
       </c>
       <c r="G6" s="5">
         <v>414</v>
       </c>
       <c r="H6" s="5">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>-0.5025788962191692</v>
+      </c>
+      <c r="O6" s="5">
+        <v>408</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1100659799055139</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.105922066761164</v>
+      </c>
+      <c r="R6" s="5">
+        <v>408</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
-        <v>0.5869560280937205</v>
+        <v>0.6351850714857872</v>
       </c>
       <c r="C7" s="4">
-        <v>0.5859619123285809</v>
+        <v>0.6351850714857872</v>
       </c>
       <c r="D7" s="4">
-        <v>0.5860116337094031</v>
+        <v>0.6327458375119489</v>
       </c>
       <c r="E7" s="4">
-        <v>78.96808965131946</v>
+        <v>83.12958033454927</v>
       </c>
       <c r="F7" s="4">
-        <v>86.70489792389455</v>
+        <v>89.08480044094273</v>
       </c>
       <c r="G7" s="5">
         <v>414</v>
       </c>
       <c r="H7" s="5">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.6351850714857872</v>
+      </c>
+      <c r="O7" s="5">
+        <v>414</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.07955722098777254</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.07955722098777254</v>
+      </c>
+      <c r="R7" s="5">
+        <v>414</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
-        <v>0.6351850714857872</v>
+        <v>0.6020871478541189</v>
       </c>
       <c r="C8" s="4">
-        <v>0.6351850714857872</v>
+        <v>0.5999431218739132</v>
       </c>
       <c r="D8" s="4">
-        <v>0.6327458375119489</v>
+        <v>0.6009939719080365</v>
       </c>
       <c r="E8" s="4">
-        <v>83.12958033454927</v>
+        <v>86.06181603076007</v>
       </c>
       <c r="F8" s="4">
-        <v>89.08480044094273</v>
+        <v>90.96537301818893</v>
       </c>
       <c r="G8" s="5">
         <v>414</v>
       </c>
       <c r="H8" s="5">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -2685,133 +4830,205 @@
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.5999431218739132</v>
+      </c>
+      <c r="O8" s="5">
+        <v>413</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.08382734950802467</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.08188110397219622</v>
+      </c>
+      <c r="R8" s="5">
+        <v>413</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
-        <v>0.5002520384031504</v>
+        <v>0.4147537809294656</v>
       </c>
       <c r="C9" s="4">
-        <v>0.5020186524035499</v>
+        <v>0.4143966357689273</v>
       </c>
       <c r="D9" s="4">
-        <v>0.5038475682994127</v>
+        <v>0.4176679751630732</v>
       </c>
       <c r="E9" s="4">
-        <v>84.31175851983306</v>
+        <v>89.94166748825137</v>
       </c>
       <c r="F9" s="4">
-        <v>89.15215770190966</v>
+        <v>92.91640999038148</v>
       </c>
       <c r="G9" s="5">
         <v>414</v>
       </c>
       <c r="H9" s="5">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="I9" s="5">
         <v>0</v>
       </c>
       <c r="J9" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>-0.4143966357689273</v>
+      </c>
+      <c r="O9" s="5">
+        <v>410</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.07900066593506029</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.07880207912750747</v>
+      </c>
+      <c r="R9" s="5">
+        <v>410</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>1.526235772642234</v>
+        <v>0.7295545378213115</v>
       </c>
       <c r="C10" s="4">
-        <v>1.433599308608975</v>
+        <v>0.7255903744566189</v>
       </c>
       <c r="D10" s="4">
-        <v>1.516938497931733</v>
+        <v>0.7131436194749189</v>
       </c>
       <c r="E10" s="4">
-        <v>84.43763219573519</v>
+        <v>83.10981535471346</v>
       </c>
       <c r="F10" s="4">
-        <v>88.22702235256378</v>
+        <v>87.51287763427538</v>
       </c>
       <c r="G10" s="5">
         <v>238</v>
       </c>
       <c r="H10" s="5">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="K10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M10" s="5">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-0.7248238018361433</v>
+      </c>
+      <c r="O10" s="5">
+        <v>221</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.2157444358536554</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1987272340544151</v>
+      </c>
+      <c r="R10" s="5">
+        <v>221</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>0.7295545378213115</v>
+        <v>1.526235772642234</v>
       </c>
       <c r="C11" s="4">
-        <v>0.7255903744566189</v>
+        <v>1.433599308608975</v>
       </c>
       <c r="D11" s="4">
-        <v>0.7131436194749189</v>
+        <v>1.516938497931733</v>
       </c>
       <c r="E11" s="4">
-        <v>83.10981535471346</v>
+        <v>84.43763219573519</v>
       </c>
       <c r="F11" s="4">
-        <v>87.51287763427538</v>
+        <v>88.22702235256378</v>
       </c>
       <c r="G11" s="5">
         <v>238</v>
       </c>
       <c r="H11" s="5">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="I11" s="5">
         <v>0</v>
       </c>
       <c r="J11" s="5">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="K11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="N11" s="4">
+        <v>-1.54023234722436</v>
+      </c>
+      <c r="O11" s="5">
+        <v>218</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.3083070406102286</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.2993808259387522</v>
+      </c>
+      <c r="R11" s="5">
+        <v>218</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4">
         <v>0.6215150222982113</v>
@@ -2849,10 +5066,28 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-0.606019950465934</v>
+      </c>
+      <c r="O12" s="5">
+        <v>235</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.223454001746433</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.2225384955186472</v>
+      </c>
+      <c r="R12" s="5">
+        <v>235</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4">
         <v>0.5472857580534211</v>
@@ -2890,9 +5125,27 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
+      <c r="N13" s="4">
+        <v>-0.5480587983893827</v>
+      </c>
+      <c r="O13" s="5">
+        <v>236</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.06750771902491151</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.06703750309207261</v>
+      </c>
+      <c r="R13" s="5">
+        <v>236</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2903,14 +5156,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2921,9 +5175,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -2957,8 +5217,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2980,92 +5248,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1665757835079753</v>
+        <v>0.373768620582302</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1665757835079753</v>
+        <v>0.3712130495827332</v>
       </c>
       <c r="D3" s="4">
-        <v>0.165095583972648</v>
+        <v>0.382202473952858</v>
       </c>
       <c r="E3" s="4">
-        <v>86.41690492622169</v>
+        <v>80.40454829274704</v>
       </c>
       <c r="F3" s="4">
-        <v>89.84361659587798</v>
+        <v>86.26433334414172</v>
       </c>
       <c r="G3" s="5">
         <v>414</v>
       </c>
       <c r="H3" s="5">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3709971248067856</v>
+      </c>
+      <c r="O3" s="5">
+        <v>408</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1035720186326998</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.100489292748836</v>
+      </c>
+      <c r="R3" s="5">
+        <v>408</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3150814850220177</v>
+        <v>0.3930450449700157</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3154116180050641</v>
+        <v>0.3903023150888965</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2501819223639866</v>
+        <v>0.4005842101667803</v>
       </c>
       <c r="E4" s="4">
-        <v>84.25950573466108</v>
+        <v>84.69560287883193</v>
       </c>
       <c r="F4" s="4">
-        <v>87.78780166218279</v>
+        <v>88.22652898010232</v>
       </c>
       <c r="G4" s="5">
         <v>414</v>
       </c>
       <c r="H4" s="5">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3903023150888965</v>
+      </c>
+      <c r="O4" s="5">
+        <v>400</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1091702512092275</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09693889418917799</v>
+      </c>
+      <c r="R4" s="5">
+        <v>400</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>0.4500069409776432</v>
@@ -3103,256 +5425,382 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.4498935836533982</v>
+      </c>
+      <c r="O5" s="5">
+        <v>403</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09698576210891696</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09399493555161055</v>
+      </c>
+      <c r="R5" s="5">
+        <v>403</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2157543950604959</v>
+        <v>0.3150814850220177</v>
       </c>
       <c r="C6" s="4">
-        <v>0.2157543950604959</v>
+        <v>0.3154116180050641</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1896659243482165</v>
+        <v>0.2501819223639866</v>
       </c>
       <c r="E6" s="4">
-        <v>88.1014821387492</v>
+        <v>84.25950573466108</v>
       </c>
       <c r="F6" s="4">
-        <v>91.03010947919032</v>
+        <v>87.78780166218279</v>
       </c>
       <c r="G6" s="5">
         <v>414</v>
       </c>
       <c r="H6" s="5">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
+      <c r="N6" s="4">
+        <v>0.1077143730389999</v>
+      </c>
+      <c r="O6" s="5">
+        <v>402</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3005672159631488</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3003293116782189</v>
+      </c>
+      <c r="R6" s="5">
+        <v>402</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="4">
-        <v>0.373768620582302</v>
+        <v>0.4792172544803432</v>
       </c>
       <c r="C7" s="4">
-        <v>0.3712130495827332</v>
+        <v>0.4792055462793416</v>
       </c>
       <c r="D7" s="4">
-        <v>0.382202473952858</v>
+        <v>0.4873795925240973</v>
       </c>
       <c r="E7" s="4">
-        <v>80.40454829274704</v>
+        <v>84.0309408787669</v>
       </c>
       <c r="F7" s="4">
-        <v>86.26433334414172</v>
+        <v>88.05914902354951</v>
       </c>
       <c r="G7" s="5">
         <v>414</v>
       </c>
       <c r="H7" s="5">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
+      <c r="N7" s="4">
+        <v>-0.4756962971541055</v>
+      </c>
+      <c r="O7" s="5">
+        <v>413</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.1457952412712549</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.1461280228618877</v>
+      </c>
+      <c r="R7" s="5">
+        <v>413</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4">
-        <v>0.4792172544803432</v>
+        <v>0.1665757835079753</v>
       </c>
       <c r="C8" s="4">
-        <v>0.4792055462793416</v>
+        <v>0.1665757835079753</v>
       </c>
       <c r="D8" s="4">
-        <v>0.4873795925240973</v>
+        <v>0.165095583972648</v>
       </c>
       <c r="E8" s="4">
-        <v>84.0309408787669</v>
+        <v>86.41690492622169</v>
       </c>
       <c r="F8" s="4">
-        <v>88.05914902354951</v>
+        <v>89.84361659587798</v>
       </c>
       <c r="G8" s="5">
         <v>414</v>
       </c>
       <c r="H8" s="5">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
       </c>
       <c r="J8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5">
         <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
+      <c r="N8" s="4">
+        <v>-0.08534988258472534</v>
+      </c>
+      <c r="O8" s="5">
+        <v>414</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.147144641401509</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.147144641401509</v>
+      </c>
+      <c r="R8" s="5">
+        <v>414</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4">
-        <v>0.3930450449700157</v>
+        <v>0.2157543950604959</v>
       </c>
       <c r="C9" s="4">
-        <v>0.3903023150888965</v>
+        <v>0.2157543950604959</v>
       </c>
       <c r="D9" s="4">
-        <v>0.4005842101667803</v>
+        <v>0.1896659243482165</v>
       </c>
       <c r="E9" s="4">
-        <v>84.69560287883193</v>
+        <v>88.1014821387492</v>
       </c>
       <c r="F9" s="4">
-        <v>88.22652898010232</v>
+        <v>91.03010947919032</v>
       </c>
       <c r="G9" s="5">
         <v>414</v>
       </c>
       <c r="H9" s="5">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="I9" s="5">
         <v>0</v>
       </c>
       <c r="J9" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
         <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>0.03028641210147796</v>
+      </c>
+      <c r="O9" s="5">
+        <v>414</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.2133211896938596</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.2133211896938596</v>
+      </c>
+      <c r="R9" s="5">
+        <v>414</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>0.78286799443717</v>
+        <v>0.4331031131712162</v>
       </c>
       <c r="C10" s="4">
-        <v>0.7796205003213248</v>
+        <v>0.4258724173623816</v>
       </c>
       <c r="D10" s="4">
-        <v>0.7516736075644006</v>
+        <v>0.3966369228744591</v>
       </c>
       <c r="E10" s="4">
-        <v>80.36714685874321</v>
+        <v>80.94937975190092</v>
       </c>
       <c r="F10" s="4">
-        <v>83.93764217096339</v>
+        <v>84.91530840524159</v>
       </c>
       <c r="G10" s="5">
         <v>238</v>
       </c>
       <c r="H10" s="5">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="5">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="M10" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>-0.2527542492564196</v>
+      </c>
+      <c r="O10" s="5">
+        <v>216</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.3663377712170153</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.3585684653460018</v>
+      </c>
+      <c r="R10" s="5">
+        <v>216</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>0.4331031131712162</v>
+        <v>0.78286799443717</v>
       </c>
       <c r="C11" s="4">
-        <v>0.4258724173623816</v>
+        <v>0.7796205003213248</v>
       </c>
       <c r="D11" s="4">
-        <v>0.3966369228744591</v>
+        <v>0.7516736075644006</v>
       </c>
       <c r="E11" s="4">
-        <v>80.94937975190092</v>
+        <v>80.36714685874321</v>
       </c>
       <c r="F11" s="4">
-        <v>84.91530840524159</v>
+        <v>83.93764217096339</v>
       </c>
       <c r="G11" s="5">
         <v>238</v>
       </c>
       <c r="H11" s="5">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="I11" s="5">
         <v>0</v>
       </c>
       <c r="J11" s="5">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="N11" s="4">
+        <v>-0.7333241457169077</v>
+      </c>
+      <c r="O11" s="5">
+        <v>208</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.5063743634780591</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.4935406858373245</v>
+      </c>
+      <c r="R11" s="5">
+        <v>208</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4">
         <v>0.3120476990428234</v>
@@ -3390,10 +5838,28 @@
       <c r="M12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>-0.09329226875671305</v>
+      </c>
+      <c r="O12" s="5">
+        <v>237</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.2998986452638392</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.3009377467243192</v>
+      </c>
+      <c r="R12" s="5">
+        <v>237</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4">
         <v>0.2917088503917071</v>
@@ -3431,9 +5897,27 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
+      <c r="N13" s="4">
+        <v>-0.2853384231848301</v>
+      </c>
+      <c r="O13" s="5">
+        <v>237</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.1447412029297069</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.1447583503036955</v>
+      </c>
+      <c r="R13" s="5">
+        <v>237</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3444,14 +5928,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3462,9 +5947,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -3498,8 +5989,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3521,69 +6020,103 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4">
-        <v>3.895480596522193</v>
+        <v>1.115079034206021</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>1.115069207437047</v>
       </c>
       <c r="D3" s="4">
-        <v>3.895924637192216</v>
+        <v>1.116372135905711</v>
       </c>
       <c r="E3" s="4">
-        <v>91.01278823217599</v>
+        <v>84.48846003658265</v>
       </c>
       <c r="F3" s="4">
-        <v>93.68074319416597</v>
+        <v>89.77885466723475</v>
       </c>
       <c r="G3" s="5">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>308</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1.115069207437047</v>
+      </c>
+      <c r="O3" s="5">
+        <v>330</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05955562397987978</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05972623902063628</v>
+      </c>
+      <c r="R3" s="5">
+        <v>330</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4">
-        <v>4.909428427021952</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>2.452668856461583</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>4.909318797433867</v>
+        <v>2.451415346940098</v>
       </c>
       <c r="E4" s="4">
-        <v>93.05887520173235</v>
+        <v>88.46513605442178</v>
       </c>
       <c r="F4" s="4">
-        <v>94.71138924159057</v>
+        <v>91.81340883668904</v>
       </c>
       <c r="G4" s="5">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="H4" s="5">
         <v>0</v>
@@ -3592,28 +6125,44 @@
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+        <v>314</v>
+      </c>
+      <c r="N4" s="4">
+        <v>2.452362497347464</v>
+      </c>
+      <c r="O4" s="5">
+        <v>314</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06689110611525687</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06344815478827606</v>
+      </c>
+      <c r="R4" s="5">
+        <v>314</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
         <v>2.845800858411285</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>2.84816284313809</v>
       </c>
@@ -3644,256 +6193,374 @@
       <c r="M5" s="5">
         <v>319</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>2.84391394422454</v>
+      </c>
+      <c r="O5" s="5">
+        <v>319</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04248708536547681</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04072791108113287</v>
+      </c>
+      <c r="R5" s="5">
+        <v>319</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B6" s="4">
+        <v>4.909428427021952</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>4.909318797433867</v>
+      </c>
+      <c r="E6" s="4">
+        <v>93.05887520173235</v>
+      </c>
+      <c r="F6" s="4">
+        <v>94.71138924159057</v>
+      </c>
+      <c r="G6" s="5">
+        <v>333</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>333</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>333</v>
+      </c>
+      <c r="N6" s="4">
+        <v>4.909428427021952</v>
+      </c>
+      <c r="O6" s="5">
+        <v>333</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.06795850354278737</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.06795850354278737</v>
+      </c>
+      <c r="R6" s="5">
+        <v>333</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1.463198743224777</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.463198743224777</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1.46498883643737</v>
+      </c>
+      <c r="E7" s="4">
+        <v>86.70835407333665</v>
+      </c>
+      <c r="F7" s="4">
+        <v>91.19454902602718</v>
+      </c>
+      <c r="G7" s="5">
+        <v>328</v>
+      </c>
+      <c r="H7" s="5">
+        <v>328</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1.463198743224777</v>
+      </c>
+      <c r="O7" s="5">
+        <v>328</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0.05400022150294028</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.05400022150294028</v>
+      </c>
+      <c r="R7" s="5">
+        <v>328</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3.895480596522193</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4">
+        <v>3.895924637192216</v>
+      </c>
+      <c r="E8" s="4">
+        <v>91.01278823217599</v>
+      </c>
+      <c r="F8" s="4">
+        <v>93.68074319416597</v>
+      </c>
+      <c r="G8" s="5">
+        <v>308</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>308</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>308</v>
+      </c>
+      <c r="N8" s="4">
+        <v>3.895480596522193</v>
+      </c>
+      <c r="O8" s="5">
+        <v>308</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0.05606977582885682</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0.05606977582885682</v>
+      </c>
+      <c r="R8" s="5">
+        <v>308</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="4">
         <v>1.912298585609388</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C9" s="4">
         <v>1.896477692324857</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D9" s="4">
         <v>1.910844788099322</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E9" s="4">
         <v>93.5375193021995</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F9" s="4">
         <v>95.10571499155876</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G9" s="5">
         <v>326</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H9" s="5">
         <v>293</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
         <v>33</v>
       </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
         <v>2</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M9" s="5">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1.115079034206021</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1.115069207437047</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1.116372135905711</v>
-      </c>
-      <c r="E7" s="4">
-        <v>84.48846003658265</v>
-      </c>
-      <c r="F7" s="4">
-        <v>89.77885466723475</v>
-      </c>
-      <c r="G7" s="5">
-        <v>331</v>
-      </c>
-      <c r="H7" s="5">
-        <v>330</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>1</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4">
-        <v>1.463198743224777</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1.463198743224777</v>
-      </c>
-      <c r="D8" s="4">
-        <v>1.46498883643737</v>
-      </c>
-      <c r="E8" s="4">
-        <v>86.70835407333665</v>
-      </c>
-      <c r="F8" s="4">
-        <v>91.19454902602718</v>
-      </c>
-      <c r="G8" s="5">
-        <v>328</v>
-      </c>
-      <c r="H8" s="5">
-        <v>328</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4">
-        <v>2.452668856461583</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>2.451415346940098</v>
-      </c>
-      <c r="E9" s="4">
-        <v>88.46513605442178</v>
-      </c>
-      <c r="F9" s="4">
-        <v>91.81340883668904</v>
-      </c>
-      <c r="G9" s="5">
-        <v>320</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>320</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>6</v>
-      </c>
-      <c r="M9" s="5">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
+      <c r="N9" s="4">
+        <v>1.912028036577485</v>
+      </c>
+      <c r="O9" s="5">
+        <v>324</v>
+      </c>
+      <c r="P9" s="4">
+        <v>0.05482143682733274</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.05484154288293838</v>
+      </c>
+      <c r="R9" s="5">
+        <v>324</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4">
-        <v>7.631484318083713</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
+        <v>7.693050595349988</v>
+      </c>
+      <c r="C10" s="4"/>
       <c r="D10" s="4">
-        <v>7.633026436092289</v>
+        <v>7.699721695542588</v>
       </c>
       <c r="E10" s="4">
-        <v>88.46843765439137</v>
+        <v>88.28665910808813</v>
       </c>
       <c r="F10" s="4">
-        <v>91.29054028720313</v>
+        <v>91.60048471289853</v>
       </c>
       <c r="G10" s="5">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H10" s="5">
         <v>0</v>
       </c>
       <c r="I10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K10" s="5">
         <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M10" s="5">
         <v>173</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="N10" s="4">
+        <v>7.692962484997959</v>
+      </c>
+      <c r="O10" s="5">
+        <v>173</v>
+      </c>
+      <c r="P10" s="4">
+        <v>0.1683768018630345</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.1673262614299886</v>
+      </c>
+      <c r="R10" s="5">
+        <v>173</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B11" s="4">
-        <v>7.693050595349988</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
+        <v>7.631484318083713</v>
+      </c>
+      <c r="C11" s="4"/>
       <c r="D11" s="4">
-        <v>7.699721695542588</v>
+        <v>7.633026436092289</v>
       </c>
       <c r="E11" s="4">
-        <v>88.28665910808813</v>
+        <v>88.46843765439137</v>
       </c>
       <c r="F11" s="4">
-        <v>91.60048471289853</v>
+        <v>91.29054028720313</v>
       </c>
       <c r="G11" s="5">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
       </c>
       <c r="I11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="5">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M11" s="5">
         <v>173</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="N11" s="4">
+        <v>7.624360256557204</v>
+      </c>
+      <c r="O11" s="5">
+        <v>173</v>
+      </c>
+      <c r="P11" s="4">
+        <v>0.2831221957671433</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.2789880228888783</v>
+      </c>
+      <c r="R11" s="5">
+        <v>173</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B12" s="4">
         <v>2.161418645217194</v>
@@ -3931,10 +6598,28 @@
       <c r="M12" s="5">
         <v>148</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
+      <c r="N12" s="4">
+        <v>2.161934335563355</v>
+      </c>
+      <c r="O12" s="5">
+        <v>184</v>
+      </c>
+      <c r="P12" s="4">
+        <v>0.1637044466227908</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>0.1649625471057235</v>
+      </c>
+      <c r="R12" s="5">
+        <v>184</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4">
         <v>1.493159481661662</v>
@@ -3972,9 +6657,27 @@
       <c r="M13" s="5">
         <v>0</v>
       </c>
+      <c r="N13" s="4">
+        <v>-1.494257533752299</v>
+      </c>
+      <c r="O13" s="5">
+        <v>186</v>
+      </c>
+      <c r="P13" s="4">
+        <v>0.03619542299386908</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>0.03528606644572228</v>
+      </c>
+      <c r="R13" s="5">
+        <v>186</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3985,547 +6688,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6091795622448668</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6088679874994194</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6075577839213799</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.68582602122974</v>
-      </c>
-      <c r="F3" s="4">
-        <v>90.16346226588432</v>
-      </c>
-      <c r="G3" s="5">
-        <v>414</v>
-      </c>
-      <c r="H3" s="5">
-        <v>412</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.455827709023149</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4555737818845641</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4536994611019958</v>
-      </c>
-      <c r="E4" s="4">
-        <v>88.2406585822735</v>
-      </c>
-      <c r="F4" s="4">
-        <v>91.90107966151191</v>
-      </c>
-      <c r="G4" s="5">
-        <v>414</v>
-      </c>
-      <c r="H4" s="5">
-        <v>410</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1378598067940482</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1308865974339846</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1289138802666049</v>
-      </c>
-      <c r="E5" s="4">
-        <v>82.37889841927164</v>
-      </c>
-      <c r="F5" s="4">
-        <v>88.70308227690884</v>
-      </c>
-      <c r="G5" s="5">
-        <v>414</v>
-      </c>
-      <c r="H5" s="5">
-        <v>408</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>5</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>5</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.4475448117795867</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.4478868299638068</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.4462560962221884</v>
-      </c>
-      <c r="E6" s="4">
-        <v>86.16130993460187</v>
-      </c>
-      <c r="F6" s="4">
-        <v>90.7109392730934</v>
-      </c>
-      <c r="G6" s="5">
-        <v>414</v>
-      </c>
-      <c r="H6" s="5">
-        <v>412</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>2</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>2</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="25" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.5188554135710317</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.5184973090486337</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0.5146573629451394</v>
-      </c>
-      <c r="E7" s="4">
-        <v>75.82158467251635</v>
-      </c>
-      <c r="F7" s="4">
-        <v>84.75464448983631</v>
-      </c>
-      <c r="G7" s="5">
-        <v>414</v>
-      </c>
-      <c r="H7" s="5">
-        <v>411</v>
-      </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5">
-        <v>3</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>3</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="25" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4">
-        <v>0.6169236078604531</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.6169236078604531</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.6111909271538402</v>
-      </c>
-      <c r="E8" s="4">
-        <v>79.79008511617208</v>
-      </c>
-      <c r="F8" s="4">
-        <v>87.30252137167805</v>
-      </c>
-      <c r="G8" s="5">
-        <v>414</v>
-      </c>
-      <c r="H8" s="5">
-        <v>414</v>
-      </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="25" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0.5648652027308053</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.5616925886059562</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.5643310604606337</v>
-      </c>
-      <c r="E9" s="4">
-        <v>80.17976272634623</v>
-      </c>
-      <c r="F9" s="4">
-        <v>86.47656410422874</v>
-      </c>
-      <c r="G9" s="5">
-        <v>414</v>
-      </c>
-      <c r="H9" s="5">
-        <v>400</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>14</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>14</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4">
-        <v>0.7254275845013083</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0.7316886342649053</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.7132414449795202</v>
-      </c>
-      <c r="E10" s="4">
-        <v>81.74555536500328</v>
-      </c>
-      <c r="F10" s="4">
-        <v>87.16569849415995</v>
-      </c>
-      <c r="G10" s="5">
-        <v>238</v>
-      </c>
-      <c r="H10" s="5">
-        <v>221</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>17</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <v>17</v>
-      </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="25" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.606762317594003</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.5883905509432389</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.5771975737944819</v>
-      </c>
-      <c r="E11" s="4">
-        <v>80.92837134853963</v>
-      </c>
-      <c r="F11" s="4">
-        <v>86.583667023855</v>
-      </c>
-      <c r="G11" s="5">
-        <v>238</v>
-      </c>
-      <c r="H11" s="5">
-        <v>221</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>17</v>
-      </c>
-      <c r="K11" s="5">
-        <v>1</v>
-      </c>
-      <c r="L11" s="5">
-        <v>16</v>
-      </c>
-      <c r="M11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0.3632485900840341</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0.3669408583029517</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.3656999707447172</v>
-      </c>
-      <c r="E12" s="4">
-        <v>82.61618933287602</v>
-      </c>
-      <c r="F12" s="4">
-        <v>88.98905871073214</v>
-      </c>
-      <c r="G12" s="5">
-        <v>238</v>
-      </c>
-      <c r="H12" s="5">
-        <v>235</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <v>3</v>
-      </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <v>3</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0.3985710691711827</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0.3990836960834979</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.393713282330131</v>
-      </c>
-      <c r="E13" s="4">
-        <v>82.35608529125938</v>
-      </c>
-      <c r="F13" s="4">
-        <v>88.50328050683365</v>
-      </c>
-      <c r="G13" s="5">
-        <v>238</v>
-      </c>
-      <c r="H13" s="5">
-        <v>237</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>1</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" s="5">
-        <v>1</v>
-      </c>
-      <c r="M13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/RolingBimetallic2017.xlsx
+++ b/public/downloads/RolingBimetallic2017.xlsx
@@ -1095,16 +1095,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5184973090486337</v>
+        <v>-0.5145982954469228</v>
       </c>
       <c r="O3" s="5">
         <v>411</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0752053755855214</v>
+        <v>0.07512624725656065</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07539360150883963</v>
+        <v>0.07528543564753823</v>
       </c>
       <c r="R3" s="5">
         <v>411</v>
@@ -1154,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5616925886059562</v>
+        <v>-0.5692163964820638</v>
       </c>
       <c r="O4" s="5">
         <v>400</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08731094997863934</v>
+        <v>0.08716170384068318</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07688477173461215</v>
+        <v>0.07665506390306648</v>
       </c>
       <c r="R4" s="5">
         <v>400</v>
@@ -1213,16 +1213,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1242944072788553</v>
+        <v>-0.1274189771324419</v>
       </c>
       <c r="O5" s="5">
         <v>408</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07816075752596079</v>
+        <v>0.07810298189326027</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0693761352816516</v>
+        <v>0.06928687696951347</v>
       </c>
       <c r="R5" s="5">
         <v>408</v>
@@ -1272,16 +1272,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4555737818845641</v>
+        <v>-0.4686751002885714</v>
       </c>
       <c r="O6" s="5">
         <v>410</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1053761396906299</v>
+        <v>0.1047310512584251</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1038553732898776</v>
+        <v>0.1032039913119928</v>
       </c>
       <c r="R6" s="5">
         <v>410</v>
@@ -1331,16 +1331,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.6169236078604531</v>
+        <v>-0.6207241379080328</v>
       </c>
       <c r="O7" s="5">
         <v>414</v>
       </c>
       <c r="P7" s="4">
-        <v>0.07399027816554271</v>
+        <v>0.07389992018304221</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.07399027816554271</v>
+        <v>0.07389992018304221</v>
       </c>
       <c r="R7" s="5">
         <v>414</v>
@@ -1390,16 +1390,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.6088679874994194</v>
+        <v>-0.6193593654605323</v>
       </c>
       <c r="O8" s="5">
         <v>412</v>
       </c>
       <c r="P8" s="4">
-        <v>0.0769864178802785</v>
+        <v>0.07639541607203051</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.07704705111121377</v>
+        <v>0.07650410938137774</v>
       </c>
       <c r="R8" s="5">
         <v>412</v>
@@ -1449,16 +1449,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4478868299638068</v>
+        <v>-0.4703326334797211</v>
       </c>
       <c r="O9" s="5">
         <v>412</v>
       </c>
       <c r="P9" s="4">
-        <v>0.08733630893597169</v>
+        <v>0.08586292731001234</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.08741659313404158</v>
+        <v>0.08582709895884984</v>
       </c>
       <c r="R9" s="5">
         <v>412</v>
@@ -1508,16 +1508,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.5840924264301415</v>
+        <v>-0.5822208092426031</v>
       </c>
       <c r="O10" s="5">
         <v>221</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2298057931934378</v>
+        <v>0.2297900653179122</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1954150931274415</v>
+        <v>0.1954066242713893</v>
       </c>
       <c r="R10" s="5">
         <v>221</v>
@@ -1567,16 +1567,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.724336472735716</v>
+        <v>-0.7173383308024546</v>
       </c>
       <c r="O11" s="5">
         <v>221</v>
       </c>
       <c r="P11" s="4">
-        <v>0.261484485882171</v>
+        <v>0.2612994245247212</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2543809865294819</v>
+        <v>0.2542560074688663</v>
       </c>
       <c r="R11" s="5">
         <v>221</v>
@@ -1626,16 +1626,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.3451128632803082</v>
+        <v>-0.3646283282379565</v>
       </c>
       <c r="O12" s="5">
         <v>235</v>
       </c>
       <c r="P12" s="4">
-        <v>0.1979437829773134</v>
+        <v>0.1971892832737575</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1964072869690227</v>
+        <v>0.1953940217591535</v>
       </c>
       <c r="R12" s="5">
         <v>235</v>
@@ -1685,16 +1685,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.3990836960834979</v>
+        <v>-0.4088745703303269</v>
       </c>
       <c r="O13" s="5">
         <v>237</v>
       </c>
       <c r="P13" s="4">
-        <v>0.0602776503404534</v>
+        <v>0.06003731188130865</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.06001719652277169</v>
+        <v>0.05973453227161861</v>
       </c>
       <c r="R13" s="5">
         <v>237</v>
@@ -1831,13 +1831,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1388211128205677</v>
+        <v>0.137744455769099</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1323196785967917</v>
+        <v>0.1309011877579991</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1403911900510892</v>
+        <v>0.1396119281810257</v>
       </c>
       <c r="K3" s="4">
         <v>84.33587772771443</v>
@@ -1881,13 +1881,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.185452740684963</v>
+        <v>0.1853902083400377</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1639882052150507</v>
+        <v>0.1635184879800908</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1773068190772146</v>
+        <v>0.1772991739196882</v>
       </c>
       <c r="K4" s="4">
         <v>80.13933209647477</v>
@@ -1931,13 +1931,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.1114985961291513</v>
+        <v>0.1110722344396003</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1066641031507543</v>
+        <v>0.106270718765971</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1112005943562614</v>
+        <v>0.1107627076356084</v>
       </c>
       <c r="K5" s="4">
         <v>84.35158582913679</v>
@@ -1981,13 +1981,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2015023606554979</v>
+        <v>0.2013244752638344</v>
       </c>
       <c r="I6" s="4">
-        <v>0.1955513020040301</v>
+        <v>0.1953619046882874</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1886268643923585</v>
+        <v>0.1885386502939885</v>
       </c>
       <c r="K6" s="4">
         <v>83.78498984009188</v>
@@ -2031,13 +2031,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.08282890307499147</v>
+        <v>0.08269598755640237</v>
       </c>
       <c r="I7" s="4">
-        <v>0.08147162735895155</v>
+        <v>0.08134781527279679</v>
       </c>
       <c r="J7" s="4">
-        <v>0.08269626877643337</v>
+        <v>0.08256813540059298</v>
       </c>
       <c r="K7" s="4">
         <v>88.79582766439866</v>
@@ -2081,13 +2081,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.1091717937255368</v>
+        <v>0.108766039175183</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1033595777215337</v>
+        <v>0.1029125013282644</v>
       </c>
       <c r="J8" s="4">
-        <v>0.107101278043049</v>
+        <v>0.1067761619725538</v>
       </c>
       <c r="K8" s="4">
         <v>82.32848308154443</v>
@@ -2992,16 +2992,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6171568810984206</v>
+        <v>-0.595896933142539</v>
       </c>
       <c r="O3" s="5">
         <v>410</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1048481294829384</v>
+        <v>0.1035887565696856</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1031549369442885</v>
+        <v>0.1017795704028289</v>
       </c>
       <c r="R3" s="5">
         <v>410</v>
@@ -3051,16 +3051,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3386690345142478</v>
+        <v>-0.3335915089172461</v>
       </c>
       <c r="O4" s="5">
         <v>398</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09849228451952907</v>
+        <v>0.09838195643794821</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0876522346411326</v>
+        <v>0.08756298646379476</v>
       </c>
       <c r="R4" s="5">
         <v>398</v>
@@ -3110,16 +3110,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7565910875890168</v>
+        <v>-0.7410354944915429</v>
       </c>
       <c r="O5" s="5">
         <v>400</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09175547078466448</v>
+        <v>0.0915177338911549</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0876090614348233</v>
+        <v>0.08728522578455353</v>
       </c>
       <c r="R5" s="5">
         <v>400</v>
@@ -3169,16 +3169,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.6277738551492573</v>
+        <v>-0.625715600343506</v>
       </c>
       <c r="O6" s="5">
         <v>405</v>
       </c>
       <c r="P6" s="4">
-        <v>0.150043543400691</v>
+        <v>0.1500252856797351</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1444384593738349</v>
+        <v>0.1444248780363781</v>
       </c>
       <c r="R6" s="5">
         <v>405</v>
@@ -3228,16 +3228,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.8950465178089574</v>
+        <v>-0.9009119797601171</v>
       </c>
       <c r="O7" s="5">
         <v>414</v>
       </c>
       <c r="P7" s="4">
-        <v>0.09880561607651323</v>
+        <v>0.09864574572217655</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.09880561607651323</v>
+        <v>0.09864574572217655</v>
       </c>
       <c r="R7" s="5">
         <v>414</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3066929368724008</v>
+        <v>-0.3052280124163866</v>
       </c>
       <c r="O8" s="5">
         <v>414</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1141373922749373</v>
+        <v>0.1141256831854167</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1141373922749373</v>
+        <v>0.1141256831854167</v>
       </c>
       <c r="R8" s="5">
         <v>414</v>
@@ -3346,16 +3346,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4598708518236438</v>
+        <v>-0.4763002566752781</v>
       </c>
       <c r="O9" s="5">
         <v>410</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1090021912147836</v>
+        <v>0.1083039778662772</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.108914594878793</v>
+        <v>0.1082897131310408</v>
       </c>
       <c r="R9" s="5">
         <v>410</v>
@@ -3405,16 +3405,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-1.223503400698428</v>
+        <v>-1.276654671736226</v>
       </c>
       <c r="O10" s="5">
         <v>218</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2489867211580931</v>
+        <v>0.245214359319654</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2298870836623952</v>
+        <v>0.2236511985019194</v>
       </c>
       <c r="R10" s="5">
         <v>218</v>
@@ -3464,16 +3464,16 @@
         <v>95</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.911452387340421</v>
+        <v>-1.969561540506831</v>
       </c>
       <c r="O11" s="5">
         <v>214</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3339042878513063</v>
+        <v>0.3310976933051254</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3139127126206388</v>
+        <v>0.3083970277155345</v>
       </c>
       <c r="R11" s="5">
         <v>214</v>
@@ -3523,16 +3523,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.6275264175708274</v>
+        <v>-0.6818503980145847</v>
       </c>
       <c r="O12" s="5">
         <v>229</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2300108544581959</v>
+        <v>0.2247852334771639</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2271776876370573</v>
+        <v>0.2209215703711278</v>
       </c>
       <c r="R12" s="5">
         <v>229</v>
@@ -3582,16 +3582,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.9845304149747647</v>
+        <v>-0.9658229795012305</v>
       </c>
       <c r="O13" s="5">
         <v>237</v>
       </c>
       <c r="P13" s="4">
-        <v>0.09839329816688312</v>
+        <v>0.09712225599528293</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.09795939383459899</v>
+        <v>0.09676192294275379</v>
       </c>
       <c r="R13" s="5">
         <v>237</v>
@@ -3764,16 +3764,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3430541603041283</v>
+        <v>-0.342549411669375</v>
       </c>
       <c r="O3" s="5">
         <v>382</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1286152485115248</v>
+        <v>0.1286013292104903</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1071317388045918</v>
+        <v>0.1071298668038568</v>
       </c>
       <c r="R3" s="5">
         <v>382</v>
@@ -3823,16 +3823,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01913949341708959</v>
+        <v>0.02577088930289051</v>
       </c>
       <c r="O4" s="5">
         <v>379</v>
       </c>
       <c r="P4" s="4">
-        <v>0.125340800970456</v>
+        <v>0.1251304125070562</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.107831507787545</v>
+        <v>0.1077241699177643</v>
       </c>
       <c r="R4" s="5">
         <v>379</v>
@@ -3882,16 +3882,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4672604550334108</v>
+        <v>-0.4779532761787597</v>
       </c>
       <c r="O5" s="5">
         <v>367</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1415639921195436</v>
+        <v>0.1414570987413654</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1109497593934344</v>
+        <v>0.1105990210007334</v>
       </c>
       <c r="R5" s="5">
         <v>367</v>
@@ -3941,16 +3941,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4754017430141103</v>
+        <v>-0.4800449543770311</v>
       </c>
       <c r="O6" s="5">
         <v>386</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2058103639317244</v>
+        <v>0.2056983296340481</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1951320153239044</v>
+        <v>0.1950599703659088</v>
       </c>
       <c r="R6" s="5">
         <v>386</v>
@@ -4000,16 +4000,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4387133721418743</v>
+        <v>-0.4588633279711718</v>
       </c>
       <c r="O7" s="5">
         <v>412</v>
       </c>
       <c r="P7" s="4">
-        <v>0.134259083079741</v>
+        <v>0.1331859636918529</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1345701697910732</v>
+        <v>0.1335896564053279</v>
       </c>
       <c r="R7" s="5">
         <v>412</v>
@@ -4059,16 +4059,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3436394967250757</v>
+        <v>-0.3618875003967874</v>
       </c>
       <c r="O8" s="5">
         <v>406</v>
       </c>
       <c r="P8" s="4">
-        <v>0.1715901720914971</v>
+        <v>0.1707282524459563</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.1708752698193488</v>
+        <v>0.1699963665354722</v>
       </c>
       <c r="R8" s="5">
         <v>406</v>
@@ -4118,16 +4118,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.1861534327419868</v>
+        <v>0.1875174581046872</v>
       </c>
       <c r="O9" s="5">
         <v>401</v>
       </c>
       <c r="P9" s="4">
-        <v>0.1661804797535738</v>
+        <v>0.1661767473910462</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.1627924239848572</v>
+        <v>0.1627851690635377</v>
       </c>
       <c r="R9" s="5">
         <v>401</v>
@@ -4177,16 +4177,16 @@
         <v>2</v>
       </c>
       <c r="N10" s="4">
-        <v>-1.28007817091255</v>
+        <v>-1.316700234602119</v>
       </c>
       <c r="O10" s="5">
         <v>196</v>
       </c>
       <c r="P10" s="4">
-        <v>0.325482934968839</v>
+        <v>0.3271395899075625</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2757062423613096</v>
+        <v>0.2741650155804235</v>
       </c>
       <c r="R10" s="5">
         <v>196</v>
@@ -4236,16 +4236,16 @@
         <v>27</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.535500097217541</v>
+        <v>-1.5609887863575</v>
       </c>
       <c r="O11" s="5">
         <v>185</v>
       </c>
       <c r="P11" s="4">
-        <v>0.4268946702771889</v>
+        <v>0.4287985356896906</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3428111570419144</v>
+        <v>0.3418160367158408</v>
       </c>
       <c r="R11" s="5">
         <v>185</v>
@@ -4295,16 +4295,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.5289446822505075</v>
+        <v>-0.5503398137060938</v>
       </c>
       <c r="O12" s="5">
         <v>210</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2582030110837319</v>
+        <v>0.2584115088682583</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2371740685569465</v>
+        <v>0.2367648378941771</v>
       </c>
       <c r="R12" s="5">
         <v>210</v>
@@ -4354,16 +4354,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.7927533314546191</v>
+        <v>-0.8064128273215627</v>
       </c>
       <c r="O13" s="5">
         <v>235</v>
       </c>
       <c r="P13" s="4">
-        <v>0.1222847344579301</v>
+        <v>0.1216476545669001</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1210168663918271</v>
+        <v>0.1204297790803454</v>
       </c>
       <c r="R13" s="5">
         <v>235</v>
@@ -4536,16 +4536,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5859619123285809</v>
+        <v>-0.5856866389666924</v>
       </c>
       <c r="O3" s="5">
         <v>411</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06768773366105831</v>
+        <v>0.067687888228529</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06718043262508594</v>
+        <v>0.06717857902617401</v>
       </c>
       <c r="R3" s="5">
         <v>411</v>
@@ -4595,16 +4595,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.5020186524035499</v>
+        <v>-0.4962235007879159</v>
       </c>
       <c r="O4" s="5">
         <v>404</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07932949976023061</v>
+        <v>0.07909049389692703</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07309789000375318</v>
+        <v>0.07291034589250282</v>
       </c>
       <c r="R4" s="5">
         <v>404</v>
@@ -4654,16 +4654,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5817540741696292</v>
+        <v>-0.5786953961607262</v>
       </c>
       <c r="O5" s="5">
         <v>401</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06888047332264895</v>
+        <v>0.06883021291673738</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06361059985909026</v>
+        <v>0.06358159294133295</v>
       </c>
       <c r="R5" s="5">
         <v>401</v>
@@ -4713,16 +4713,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5025788962191692</v>
+        <v>-0.4999364402977253</v>
       </c>
       <c r="O6" s="5">
         <v>408</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1100659799055139</v>
+        <v>0.1100724759557889</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.105922066761164</v>
+        <v>0.1059027519109877</v>
       </c>
       <c r="R6" s="5">
         <v>408</v>
@@ -4772,16 +4772,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.6351850714857872</v>
+        <v>-0.6392304817623151</v>
       </c>
       <c r="O7" s="5">
         <v>414</v>
       </c>
       <c r="P7" s="4">
-        <v>0.07955722098777254</v>
+        <v>0.07945330371046162</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.07955722098777254</v>
+        <v>0.07945330371046162</v>
       </c>
       <c r="R7" s="5">
         <v>414</v>
@@ -4831,16 +4831,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.5999431218739132</v>
+        <v>-0.6002864429361958</v>
       </c>
       <c r="O8" s="5">
         <v>413</v>
       </c>
       <c r="P8" s="4">
-        <v>0.08382734950802467</v>
+        <v>0.08382569095216823</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.08188110397219622</v>
+        <v>0.08188027268633112</v>
       </c>
       <c r="R8" s="5">
         <v>413</v>
@@ -4890,16 +4890,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4143966357689273</v>
+        <v>-0.4223715766766665</v>
       </c>
       <c r="O9" s="5">
         <v>410</v>
       </c>
       <c r="P9" s="4">
-        <v>0.07900066593506029</v>
+        <v>0.078688136053275</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.07880207912750747</v>
+        <v>0.07852144421847732</v>
       </c>
       <c r="R9" s="5">
         <v>410</v>
@@ -4949,16 +4949,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.7248238018361433</v>
+        <v>-0.7387015280393623</v>
       </c>
       <c r="O10" s="5">
         <v>221</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2157444358536554</v>
+        <v>0.2154851459617501</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1987272340544151</v>
+        <v>0.1983852036450184</v>
       </c>
       <c r="R10" s="5">
         <v>221</v>
@@ -5008,16 +5008,16 @@
         <v>29</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.54023234722436</v>
+        <v>-1.507308621438235</v>
       </c>
       <c r="O11" s="5">
         <v>218</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3083070406102286</v>
+        <v>0.3067601799727452</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2993808259387522</v>
+        <v>0.2981553951207712</v>
       </c>
       <c r="R11" s="5">
         <v>218</v>
@@ -5067,16 +5067,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.606019950465934</v>
+        <v>-0.6412973768846841</v>
       </c>
       <c r="O12" s="5">
         <v>235</v>
       </c>
       <c r="P12" s="4">
-        <v>0.223454001746433</v>
+        <v>0.219922495699723</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2225384955186472</v>
+        <v>0.2191120231241867</v>
       </c>
       <c r="R12" s="5">
         <v>235</v>
@@ -5126,16 +5126,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.5480587983893827</v>
+        <v>-0.5562071164463862</v>
       </c>
       <c r="O13" s="5">
         <v>236</v>
       </c>
       <c r="P13" s="4">
-        <v>0.06750771902491151</v>
+        <v>0.06716725014272151</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.06703750309207261</v>
+        <v>0.06669414888037256</v>
       </c>
       <c r="R13" s="5">
         <v>236</v>
@@ -5308,16 +5308,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3709971248067856</v>
+        <v>-0.3745197166754322</v>
       </c>
       <c r="O3" s="5">
         <v>408</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1035720186326998</v>
+        <v>0.1035463613532465</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.100489292748836</v>
+        <v>0.1004805257636489</v>
       </c>
       <c r="R3" s="5">
         <v>408</v>
@@ -5367,16 +5367,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3903023150888965</v>
+        <v>-0.3973776954156103</v>
       </c>
       <c r="O4" s="5">
         <v>400</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1091702512092275</v>
+        <v>0.1090282577015557</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09693889418917799</v>
+        <v>0.09668580020383694</v>
       </c>
       <c r="R4" s="5">
         <v>400</v>
@@ -5426,16 +5426,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4498935836533982</v>
+        <v>-0.4512182254864405</v>
       </c>
       <c r="O5" s="5">
         <v>403</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09698576210891696</v>
+        <v>0.09697135188284102</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09399493555161055</v>
+        <v>0.0939899928516197</v>
       </c>
       <c r="R5" s="5">
         <v>403</v>
@@ -5485,16 +5485,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.1077143730389999</v>
+        <v>0.1108566076214359</v>
       </c>
       <c r="O6" s="5">
         <v>402</v>
       </c>
       <c r="P6" s="4">
-        <v>0.3005672159631488</v>
+        <v>0.3005951554010928</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.3003293116782189</v>
+        <v>0.3003268191134901</v>
       </c>
       <c r="R6" s="5">
         <v>402</v>
@@ -5544,16 +5544,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.4756962971541055</v>
+        <v>-0.4928399120096336</v>
       </c>
       <c r="O7" s="5">
         <v>413</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1457952412712549</v>
+        <v>0.1449869001082263</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1461280228618877</v>
+        <v>0.1453166815358113</v>
       </c>
       <c r="R7" s="5">
         <v>413</v>
@@ -5603,16 +5603,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.08534988258472534</v>
+        <v>-0.09090617258189448</v>
       </c>
       <c r="O8" s="5">
         <v>414</v>
       </c>
       <c r="P8" s="4">
-        <v>0.147144641401509</v>
+        <v>0.1470654027918993</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.147144641401509</v>
+        <v>0.1470654027918993</v>
       </c>
       <c r="R8" s="5">
         <v>414</v>
@@ -5662,16 +5662,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.03028641210147796</v>
+        <v>0.04414277223417962</v>
       </c>
       <c r="O9" s="5">
         <v>414</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2133211896938596</v>
+        <v>0.212929190741497</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2133211896938596</v>
+        <v>0.212929190741497</v>
       </c>
       <c r="R9" s="5">
         <v>414</v>
@@ -5721,16 +5721,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.2527542492564196</v>
+        <v>-0.2580879462409378</v>
       </c>
       <c r="O10" s="5">
         <v>216</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3663377712170153</v>
+        <v>0.3662295747483872</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.3585684653460018</v>
+        <v>0.3584986349498702</v>
       </c>
       <c r="R10" s="5">
         <v>216</v>
@@ -5780,16 +5780,16 @@
         <v>3</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.7333241457169077</v>
+        <v>-0.7300647441397952</v>
       </c>
       <c r="O11" s="5">
         <v>208</v>
       </c>
       <c r="P11" s="4">
-        <v>0.5063743634780591</v>
+        <v>0.5062648037611814</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.4935406858373245</v>
+        <v>0.4935406858373246</v>
       </c>
       <c r="R11" s="5">
         <v>208</v>
@@ -5839,16 +5839,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.09329226875671305</v>
+        <v>-0.1098774905827149</v>
       </c>
       <c r="O12" s="5">
         <v>237</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2998986452638392</v>
+        <v>0.2997327592913704</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.3009377467243192</v>
+        <v>0.30070118097211</v>
       </c>
       <c r="R12" s="5">
         <v>237</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.2853384231848301</v>
+        <v>-0.2868229414772803</v>
       </c>
       <c r="O13" s="5">
         <v>237</v>
@@ -5907,7 +5907,7 @@
         <v>0.1447412029297069</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.1447583503036955</v>
+        <v>0.144752086513432</v>
       </c>
       <c r="R13" s="5">
         <v>237</v>
@@ -6080,16 +6080,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>1.115069207437047</v>
+        <v>1.119121551408061</v>
       </c>
       <c r="O3" s="5">
         <v>330</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05955562397987978</v>
+        <v>0.05941846269585772</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05972623902063628</v>
+        <v>0.05959609536026704</v>
       </c>
       <c r="R3" s="5">
         <v>330</v>
@@ -6137,16 +6137,16 @@
         <v>314</v>
       </c>
       <c r="N4" s="4">
-        <v>2.452362497347464</v>
+        <v>2.451115168581377</v>
       </c>
       <c r="O4" s="5">
         <v>314</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06689110611525687</v>
+        <v>0.06688318824892256</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06344815478827606</v>
+        <v>0.06343214085592207</v>
       </c>
       <c r="R4" s="5">
         <v>314</v>
@@ -6194,16 +6194,16 @@
         <v>319</v>
       </c>
       <c r="N5" s="4">
-        <v>2.84391394422454</v>
+        <v>2.846410175335752</v>
       </c>
       <c r="O5" s="5">
         <v>319</v>
       </c>
       <c r="P5" s="4">
-        <v>0.04248708536547681</v>
+        <v>0.04242994678368207</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04072791108113287</v>
+        <v>0.04067806032180155</v>
       </c>
       <c r="R5" s="5">
         <v>319</v>
@@ -6251,16 +6251,16 @@
         <v>333</v>
       </c>
       <c r="N6" s="4">
-        <v>4.909428427021952</v>
+        <v>4.905928148097803</v>
       </c>
       <c r="O6" s="5">
         <v>333</v>
       </c>
       <c r="P6" s="4">
-        <v>0.06795850354278737</v>
+        <v>0.06785186533191581</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.06795850354278737</v>
+        <v>0.06785186533191581</v>
       </c>
       <c r="R6" s="5">
         <v>333</v>
@@ -6310,16 +6310,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>1.463198743224777</v>
+        <v>1.459725230800351</v>
       </c>
       <c r="O7" s="5">
         <v>328</v>
       </c>
       <c r="P7" s="4">
-        <v>0.05400022150294028</v>
+        <v>0.05390835657053592</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.05400022150294028</v>
+        <v>0.05390835657053592</v>
       </c>
       <c r="R7" s="5">
         <v>328</v>
@@ -6367,16 +6367,16 @@
         <v>308</v>
       </c>
       <c r="N8" s="4">
-        <v>3.895480596522193</v>
+        <v>3.889640581236065</v>
       </c>
       <c r="O8" s="5">
         <v>308</v>
       </c>
       <c r="P8" s="4">
-        <v>0.05606977582885682</v>
+        <v>0.05591214635138343</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.05606977582885682</v>
+        <v>0.05591214635138343</v>
       </c>
       <c r="R8" s="5">
         <v>308</v>
@@ -6426,16 +6426,16 @@
         <v>31</v>
       </c>
       <c r="N9" s="4">
-        <v>1.912028036577485</v>
+        <v>1.909212306891939</v>
       </c>
       <c r="O9" s="5">
         <v>324</v>
       </c>
       <c r="P9" s="4">
-        <v>0.05482143682733274</v>
+        <v>0.05477412407566622</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.05484154288293838</v>
+        <v>0.05479393807724924</v>
       </c>
       <c r="R9" s="5">
         <v>324</v>
@@ -6483,16 +6483,16 @@
         <v>173</v>
       </c>
       <c r="N10" s="4">
-        <v>7.692962484997959</v>
+        <v>7.679690919478515</v>
       </c>
       <c r="O10" s="5">
         <v>173</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1683768018630345</v>
+        <v>0.1676695756760999</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1673262614299886</v>
+        <v>0.1666734225756105</v>
       </c>
       <c r="R10" s="5">
         <v>173</v>
@@ -6540,16 +6540,16 @@
         <v>173</v>
       </c>
       <c r="N11" s="4">
-        <v>7.624360256557204</v>
+        <v>7.624351692108008</v>
       </c>
       <c r="O11" s="5">
         <v>173</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2831221957671433</v>
+        <v>0.2831222436132282</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2789880228888783</v>
+        <v>0.2789879733833917</v>
       </c>
       <c r="R11" s="5">
         <v>173</v>
@@ -6599,16 +6599,16 @@
         <v>148</v>
       </c>
       <c r="N12" s="4">
-        <v>2.161934335563355</v>
+        <v>2.154518264248574</v>
       </c>
       <c r="O12" s="5">
         <v>184</v>
       </c>
       <c r="P12" s="4">
-        <v>0.1637044466227908</v>
+        <v>0.1632939211208375</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1649625471057235</v>
+        <v>0.1646281688408661</v>
       </c>
       <c r="R12" s="5">
         <v>184</v>
@@ -6658,13 +6658,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-1.494257533752299</v>
+        <v>-1.4951096542775</v>
       </c>
       <c r="O13" s="5">
         <v>186</v>
       </c>
       <c r="P13" s="4">
-        <v>0.03619542299386908</v>
+        <v>0.03619997978812149</v>
       </c>
       <c r="Q13" s="4">
         <v>0.03528606644572228</v>
